--- a/eventdummy.xlsx
+++ b/eventdummy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef90ac1ebd1348f5/바탕 화면/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Living_Lab_team2\python-create-hwpfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{CD1F1EEC-1825-4469-A4C1-BEA547047AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{290B0E2F-F654-44B3-ACFA-D8BD9375EA59}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24941CB-1A1D-4C38-896D-C0531BD8E1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AB989939-B826-4B7A-A5D6-BDC29F80D499}"/>
   </bookViews>
@@ -25,20 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="57">
   <si>
     <t>예방의약과</t>
   </si>
   <si>
-    <t>40명</t>
-  </si>
-  <si>
     <t>미래전략과</t>
-  </si>
-  <si>
-    <t>4. 8.
-(월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>date</t>
@@ -87,11 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4. 9.
-(화)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대전정보문화
 산업진흥원</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,11 +101,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4. 10.
-(수)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,15 +121,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4. 11.
-(목)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아가랑도서관</t>
-  </si>
-  <si>
-    <t>10명</t>
   </si>
   <si>
     <t>구암도서관</t>
@@ -181,11 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4. 12. 
-(금)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>·2024년 공무직 산업시찰</t>
   </si>
   <si>
@@ -199,69 +168,78 @@
     <t>·마음의 병과 치유 「아픈 마음의 연원과 철학 상담」</t>
   </si>
   <si>
+    <t xml:space="preserve">2024 대청호 벚꽃길 마라톤대회 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소셜다이닝「1인 가구 함께하는 식사」(1회차)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동구 신상동 282</t>
+  </si>
+  <si>
+    <t>하기동 하하팜농장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유성문화원 1층전시실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노은도서관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어린이영어마을도서관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>·2024년 특성화 사업 제1회차‘인문학 콘서트’</t>
+  </si>
+  <si>
+    <t>·행복한 문화학교 「햄스터 로봇 코딩」</t>
+  </si>
+  <si>
+    <t>·노은도서관 동화 들려주기(Story Time)</t>
+  </si>
+  <si>
+    <t>·독서프로그램 「귀 기울여 영어동화」 영어원서 읽기</t>
+  </si>
+  <si>
+    <t>홍보실</t>
+  </si>
+  <si>
+    <t>문화관광과</t>
+  </si>
+  <si>
+    <t>24.4.8 (월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4.9 (화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4.10 (수)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4.11 (목)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4.12 (금)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">
-4. 13.
-(토)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. 14.
-(일)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2024 대청호 벚꽃길 마라톤대회 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소셜다이닝「1인 가구 함께하는 식사」(1회차)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동구 신상동 282</t>
-  </si>
-  <si>
-    <t>하기동 하하팜농장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유성문화원 1층전시실</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>노은도서관</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>어린이영어마을도서관</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>·2024년 특성화 사업 제1회차‘인문학 콘서트’</t>
-  </si>
-  <si>
-    <t>·행복한 문화학교 「햄스터 로봇 코딩」</t>
-  </si>
-  <si>
-    <t>·노은도서관 동화 들려주기(Story Time)</t>
-  </si>
-  <si>
-    <t>·독서프로그램 「귀 기울여 영어동화」 영어원서 읽기</t>
-  </si>
-  <si>
-    <t>5,000명</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>14명</t>
-  </si>
-  <si>
-    <t>홍보실</t>
-  </si>
-  <si>
-    <t>문화관광과</t>
+24.4.13 (토)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4.14 (일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -374,7 +352,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -405,40 +383,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,62 +736,62 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2">
         <v>0.375</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="5">
         <v>4</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2">
         <v>0.5625</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5">
         <v>16</v>
@@ -831,405 +800,405 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B4" s="6">
         <v>0.58333333333333337</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5">
         <v>40</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B5" s="8">
         <v>0.41666666666666669</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="10">
+        <v>20</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="11">
-        <v>20</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>19</v>
-      </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B6" s="6">
         <v>0.58333333333333337</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="5">
         <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B8" s="8">
         <v>0.39583333333333331</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="11">
+      <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10">
         <v>10</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>20</v>
+      <c r="F8" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5">
         <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2">
         <v>0.5625</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="15">
+        <v>31</v>
+      </c>
+      <c r="E11" s="13">
         <v>800</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>38</v>
+      <c r="F11" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8">
         <v>0.375</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="11">
+        <v>34</v>
+      </c>
+      <c r="E12" s="10">
         <v>85</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>42</v>
+      <c r="F12" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E13" s="5">
         <v>60</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="18">
+        <v>5000</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>47</v>
+      <c r="C15" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>58</v>
+        <v>40</v>
+      </c>
+      <c r="E15" s="5">
+        <v>30</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1">
         <v>0.41666666666666669</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>58</v>
+        <v>41</v>
+      </c>
+      <c r="E16" s="5">
+        <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="16">
+        <v>55</v>
+      </c>
+      <c r="B17" s="14">
         <v>0.41666666666666669</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>59</v>
+        <v>15</v>
+      </c>
+      <c r="E17" s="5">
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1">
         <v>0.625</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="E18" s="5">
+        <v>40</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1">
         <v>0.625</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>56</v>
+      <c r="C19" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>20</v>
+        <v>43</v>
+      </c>
+      <c r="E19" s="17">
+        <v>10</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D21" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="D22" s="18"/>
+      <c r="D22" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
